--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484688_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484688_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.9256</v>
+        <v>7.4444</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6442</v>
+        <v>4.4108</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2813</v>
+        <v>3.0336</v>
       </c>
       <c r="G2" t="n">
         <v>4.237</v>
@@ -610,13 +610,13 @@
         <v>2.9321</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4216</v>
+        <v>-0.0596</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.3276</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5158</v>
+        <v>0.2681</v>
       </c>
       <c r="V2" t="n">
         <v>2.5339</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9843</v>
+        <v>5.9324</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7023</v>
+        <v>2.5266</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2819</v>
+        <v>3.4058</v>
       </c>
       <c r="G3" t="n">
         <v>0.4987</v>
@@ -688,13 +688,13 @@
         <v>2.9321</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1271</v>
+        <v>-0.1789</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.101</v>
+        <v>-0.2767</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.026</v>
+        <v>0.0978</v>
       </c>
       <c r="V3" t="n">
         <v>3.7801</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3588</v>
+        <v>3.1472</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0371</v>
+        <v>-0.1001</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3217</v>
+        <v>3.2474</v>
       </c>
       <c r="G4" t="n">
         <v>2.0704</v>
@@ -766,13 +766,13 @@
         <v>3.1154</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1227</v>
+        <v>-0.3343</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0392</v>
+        <v>-0.1764</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0835</v>
+        <v>-0.1578</v>
       </c>
       <c r="V4" t="n">
         <v>0.3115</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5953</v>
+        <v>2.4828</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0278</v>
+        <v>-0.1095</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5675</v>
+        <v>2.5922</v>
       </c>
       <c r="G5" t="n">
         <v>2.4061</v>
@@ -844,13 +844,13 @@
         <v>3.1154</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2179</v>
+        <v>0.1054</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0709</v>
+        <v>-0.0663</v>
       </c>
       <c r="U5" t="n">
-        <v>0.147</v>
+        <v>0.1717</v>
       </c>
       <c r="V5" t="n">
         <v>-0.945</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. CASASUS GOYENECHE</t>
+          <t>D. FERNANDEZ NARRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1429</v>
+        <v>1.5878</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3984</v>
+        <v>1.5618</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.026</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8803</v>
+        <v>-1.9662</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1497</v>
+        <v>-1.418</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2694</v>
+        <v>-0.5481</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2258</v>
+        <v>-1.0487</v>
       </c>
       <c r="K6" t="n">
-        <v>2.7835</v>
+        <v>0.1084</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5577</v>
+        <v>-1.157</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6545</v>
+        <v>-0.9175</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3662</v>
+        <v>-1.5264</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2882</v>
+        <v>0.6089</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1833</v>
+        <v>0.9163</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6493</v>
+        <v>0.9163</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7024</v>
+        <v>0.4257</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6282</v>
+        <v>0.0766</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9258</v>
+        <v>0.3492</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2566</v>
+        <v>2.212</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6231</v>
+        <v>2.5339</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6335</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ NARRO</t>
+          <t>G. CASASUS GOYENECHE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4917</v>
+        <v>0.9454</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4657</v>
+        <v>0.0523</v>
       </c>
       <c r="F7" t="n">
-        <v>0.026</v>
+        <v>0.8931</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.9662</v>
+        <v>2.8803</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.418</v>
+        <v>3.1497</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5481</v>
+        <v>-0.2694</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.0487</v>
+        <v>2.2258</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1084</v>
+        <v>2.7835</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.157</v>
+        <v>-0.5577</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9175</v>
+        <v>0.6545</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5264</v>
+        <v>0.3662</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6089</v>
+        <v>0.2882</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9163</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9163</v>
+        <v>1.6493</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3296</v>
+        <v>-0.4951</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0196</v>
+        <v>0.2821</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3492</v>
+        <v>-0.7772</v>
       </c>
       <c r="V7" t="n">
-        <v>2.212</v>
+        <v>-1.2566</v>
       </c>
       <c r="W7" t="n">
-        <v>2.5339</v>
+        <v>-0.6231</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3219</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="8">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2796</v>
+        <v>-0.2041</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9311</v>
+        <v>0.5465</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6515</v>
+        <v>-0.7506</v>
       </c>
       <c r="G9" t="n">
         <v>0.3562</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4287</v>
+        <v>-0.0551</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4208</v>
+        <v>0.0362</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0078</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3219</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4404</v>
+        <v>-0.8941</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1989</v>
+        <v>-1.4297</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.5356</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5021</v>
@@ -1234,13 +1234,13 @@
         <v>2.1991</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2761</v>
+        <v>0.2702</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.101</v>
+        <v>-0.3318</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8249</v>
+        <v>0.602</v>
       </c>
       <c r="V10" t="n">
         <v>-0.945</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8419</v>
+        <v>-1.8914</v>
       </c>
       <c r="E11" t="n">
         <v>-1.322</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5199</v>
+        <v>-0.5695</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1754</v>
@@ -1312,13 +1312,13 @@
         <v>1.0995</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7661</v>
+        <v>-0.8156</v>
       </c>
       <c r="T11" t="n">
         <v>-0.2398</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5263</v>
+        <v>-0.5758</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3407</v>
+        <v>-2.0493</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7857</v>
+        <v>-1.5933</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5551</v>
+        <v>-0.456</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9777</v>
@@ -1390,13 +1390,13 @@
         <v>0.3665</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5463</v>
+        <v>-1.2549</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3854</v>
+        <v>-0.1931</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.1609</v>
+        <v>-1.0618</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.2121</v>
+        <v>-2.2829</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.1279</v>
+        <v>-3.4959</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9157999999999999</v>
+        <v>1.2131</v>
       </c>
       <c r="G13" t="n">
         <v>-2.4834</v>
@@ -1468,13 +1468,13 @@
         <v>2.7489</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.4775</v>
+        <v>-1.5483</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2662</v>
+        <v>-0.6342</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.2113</v>
+        <v>-0.914</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6335</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>14.5682</v>
+        <v>14.8433</v>
       </c>
       <c r="E14" t="n">
-        <v>1.397199999999999</v>
+        <v>1.6726</v>
       </c>
       <c r="F14" t="n">
-        <v>13.1708</v>
+        <v>13.1707</v>
       </c>
       <c r="G14" t="n">
         <v>3.968999999999999</v>
@@ -1546,10 +1546,10 @@
         <v>21.0746</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.2156</v>
+        <v>-3.9405</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.1265</v>
+        <v>-1.851</v>
       </c>
       <c r="U14" t="n">
         <v>-2.0891</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.1382</v>
+        <v>6.4693</v>
       </c>
       <c r="E15" t="n">
         <v>4.3075</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8306</v>
+        <v>2.1618</v>
       </c>
       <c r="G15" t="n">
         <v>4.6106</v>
@@ -1624,13 +1624,13 @@
         <v>1.4661</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9387</v>
+        <v>1.2698</v>
       </c>
       <c r="T15" t="n">
         <v>0.6026</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3361</v>
+        <v>0.6672</v>
       </c>
       <c r="V15" t="n">
         <v>0.9554</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7101</v>
+        <v>2.1195</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6294</v>
+        <v>1.014</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0807</v>
+        <v>1.1055</v>
       </c>
       <c r="G16" t="n">
         <v>0.6568000000000001</v>
@@ -1702,13 +1702,13 @@
         <v>0.9163</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1848</v>
+        <v>0.2245</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5694</v>
+        <v>-0.1847</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3845</v>
+        <v>0.4093</v>
       </c>
       <c r="V16" t="n">
         <v>0.3219</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. CASADO SEGURA</t>
+          <t>G. BORREGA BERTOLIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7342</v>
+        <v>-0.4357</v>
       </c>
       <c r="E18" t="n">
-        <v>1.65</v>
+        <v>-0.8472</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.3842</v>
+        <v>0.4115</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2642</v>
+        <v>1.9727</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6465</v>
+        <v>1.0205</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9108000000000001</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>2.0091</v>
+        <v>2.9882</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9257</v>
+        <v>2.2601</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0833</v>
+        <v>0.7282</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.2733</v>
+        <v>-1.0155</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2792</v>
+        <v>-1.2395</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9941</v>
+        <v>0.224</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.5498</v>
+        <v>-2.0158</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8326</v>
+        <v>-3.6651</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2828</v>
+        <v>1.6493</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3364</v>
+        <v>-0.0914</v>
       </c>
       <c r="T18" t="n">
-        <v>1.4631</v>
+        <v>0.1309</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1267</v>
+        <v>-0.2223</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2566</v>
+        <v>-0.3011</v>
       </c>
       <c r="W18" t="n">
-        <v>0.0104</v>
+        <v>-0.3011</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. BORREGA BERTOLIN</t>
+          <t>J. CASADO SEGURA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3872</v>
+        <v>-1.7365</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.328</v>
+        <v>0.4</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0592</v>
+        <v>-2.1365</v>
       </c>
       <c r="G19" t="n">
-        <v>1.9727</v>
+        <v>-0.2642</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0205</v>
+        <v>0.6465</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9520999999999999</v>
+        <v>-0.9108000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9882</v>
+        <v>2.0091</v>
       </c>
       <c r="K19" t="n">
-        <v>2.2601</v>
+        <v>1.9257</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7282</v>
+        <v>0.0833</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0155</v>
+        <v>-2.2733</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2395</v>
+        <v>-1.2792</v>
       </c>
       <c r="O19" t="n">
-        <v>0.224</v>
+        <v>-0.9941</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.0158</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.6651</v>
+        <v>-1.8326</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6493</v>
+        <v>1.2828</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0429</v>
+        <v>0.3341</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3499</v>
+        <v>0.2131</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6929999999999999</v>
+        <v>0.121</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3011</v>
+        <v>-1.2566</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3011</v>
+        <v>0.0104</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.902</v>
+        <v>-2.3975</v>
       </c>
       <c r="E20" t="n">
         <v>-3.164</v>
       </c>
       <c r="F20" t="n">
-        <v>1.262</v>
+        <v>0.7665</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9294</v>
@@ -2014,13 +2014,13 @@
         <v>1.4661</v>
       </c>
       <c r="S20" t="n">
-        <v>1.5588</v>
+        <v>1.0633</v>
       </c>
       <c r="T20" t="n">
         <v>0.7127</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8461</v>
+        <v>0.3506</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3324</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9906</v>
+        <v>-2.4306</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2794</v>
+        <v>-1.4717</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7112000000000001</v>
+        <v>-0.9589</v>
       </c>
       <c r="G21" t="n">
         <v>-0.2213</v>
@@ -2092,13 +2092,13 @@
         <v>0.1833</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.0735</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0905</v>
+        <v>-0.1018</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4231</v>
+        <v>0.1753</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6335</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. VERGARA APARICIO</t>
+          <t>I. ALONSO QUINZA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0478</v>
+        <v>-2.4319</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5139</v>
+        <v>-1.6434</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5339</v>
+        <v>-0.7885</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.1723</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1976</v>
+        <v>0.5525</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9747</v>
+        <v>-0.4839</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2545</v>
+        <v>0.3467</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6968</v>
+        <v>2.1766</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5577</v>
+        <v>-1.8299</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9177999999999999</v>
+        <v>-0.2781</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5008</v>
+        <v>-1.6241</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.417</v>
+        <v>1.346</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3665</v>
+        <v>-0.733</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4661</v>
+        <v>1.0995</v>
       </c>
       <c r="S22" t="n">
-        <v>1.4465</v>
+        <v>-0.1785</v>
       </c>
       <c r="T22" t="n">
-        <v>1.5732</v>
+        <v>-0.1576</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1267</v>
+        <v>-0.021</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9554</v>
+        <v>-1.5889</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.9554</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. ALONSO QUINZA</t>
+          <t>J. VERGARA APARICIO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2813</v>
+        <v>-2.8578</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2203</v>
+        <v>-2.5716</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.061</v>
+        <v>-0.2862</v>
       </c>
       <c r="G23" t="n">
-        <v>0.06859999999999999</v>
+        <v>-2.1723</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5525</v>
+        <v>-1.1976</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4839</v>
+        <v>-0.9747</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3467</v>
+        <v>-1.2545</v>
       </c>
       <c r="K23" t="n">
-        <v>2.1766</v>
+        <v>-0.6968</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.8299</v>
+        <v>-0.5577</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2781</v>
+        <v>-0.9177999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.6241</v>
+        <v>-0.5008</v>
       </c>
       <c r="O23" t="n">
-        <v>1.346</v>
+        <v>-0.417</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.733</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R23" t="n">
-        <v>1.0995</v>
+        <v>1.4661</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.028</v>
+        <v>0.6365</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7345</v>
+        <v>0.5155</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2935</v>
+        <v>0.121</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.5889</v>
+        <v>-0.9554</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.5889</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.0142</v>
+        <v>-5.2638</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.8025</v>
+        <v>-7.2256</v>
       </c>
       <c r="F24" t="n">
-        <v>1.7883</v>
+        <v>1.9617</v>
       </c>
       <c r="G24" t="n">
         <v>-5.5717</v>
@@ -2326,13 +2326,13 @@
         <v>0.733</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3351</v>
+        <v>1.0854</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1267</v>
+        <v>0.7036</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2084</v>
+        <v>0.3818</v>
       </c>
       <c r="V24" t="n">
         <v>0.3219</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.6843</v>
+        <v>-6.2283</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.7082</v>
+        <v>-3.2274</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.9761</v>
+        <v>-3.0009</v>
       </c>
       <c r="G25" t="n">
         <v>-2.7439</v>
@@ -2404,13 +2404,13 @@
         <v>0.733</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6575</v>
+        <v>-0.2015</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8258</v>
+        <v>-0.345</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1682</v>
+        <v>0.1435</v>
       </c>
       <c r="V25" t="n">
         <v>-1.267</v>
@@ -2446,16 +2446,16 @@
         <v>-0.7640000000000002</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.968999999999999</v>
+        <v>-3.969</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.006800000000001</v>
+        <v>-3.0068</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.9623999999999995</v>
+        <v>-0.9623999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>2.6055</v>
+        <v>2.605499999999998</v>
       </c>
       <c r="K26" t="n">
         <v>6.2895</v>
@@ -2464,7 +2464,7 @@
         <v>-3.6841</v>
       </c>
       <c r="M26" t="n">
-        <v>-6.5746</v>
+        <v>-6.574599999999999</v>
       </c>
       <c r="N26" t="n">
         <v>-9.2964</v>
@@ -2482,13 +2482,13 @@
         <v>10.9955</v>
       </c>
       <c r="S26" t="n">
-        <v>4.2159</v>
+        <v>4.215699999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>2.0892</v>
+        <v>2.089300000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>2.1265</v>
+        <v>2.1264</v>
       </c>
       <c r="V26" t="n">
         <v>-4.7357</v>
